--- a/model_predictions.xlsx
+++ b/model_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ReeaL</t>
+          <t>HyDra</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7760333682997272</v>
+        <v>0.6662262518038523</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7758002796368322</v>
+        <v>0.6562950658429247</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.7957137941103468</v>
+        <v>0.7462221375391271</v>
       </c>
     </row>
     <row r="3">
@@ -537,11 +537,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vikul</t>
+          <t>KiSMET</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6878492656101436</v>
+        <v>0.6297054823618405</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.6992746053267079</v>
+        <v>0.6256624296193664</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.612023637963435</v>
+        <v>0.5252894103690796</v>
       </c>
     </row>
     <row r="4">
@@ -581,7 +581,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MettalZ</t>
+          <t>Sib</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -593,15 +593,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.5825073641713004</v>
+        <v>0.6218509610872739</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.5770237607172013</v>
+        <v>0.6088542434285625</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5433840342504523</v>
+        <v>0.52565891707337</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Skyz</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -637,23 +637,23 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.5219694676038281</v>
+        <v>0.5391527778585109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5284314868692943</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Over</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0.6522393426881622</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Over</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>0.5102170297730857</v>
+        <v>0.5242242033654626</v>
       </c>
     </row>
     <row r="6">
@@ -669,11 +669,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JoeDeceives</t>
+          <t>Pred</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.7559817475362735</v>
+        <v>0.6262706869577696</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.7857211819435601</v>
+        <v>0.6496612282688699</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7986173071498974</v>
+        <v>0.7628359608849623</v>
       </c>
     </row>
     <row r="7">
@@ -713,11 +713,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kremp</t>
+          <t>Shotzzy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.5812276013582772</v>
+        <v>0.6352929617870586</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.5321822930729577</v>
+        <v>0.6126445204598463</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.5358026936549268</v>
+        <v>0.607967119419249</v>
       </c>
     </row>
     <row r="8">
@@ -757,11 +757,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ghosty</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.749925651663667</v>
+        <v>0.5833578897026984</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.6292007452302621</v>
+        <v>0.6553338425070275</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.5639645991254223</v>
+        <v>0.5656894742228511</v>
       </c>
     </row>
     <row r="9">
@@ -801,11 +801,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nastie</t>
+          <t>Dashy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.5834424333235875</v>
+        <v>0.6081475686899058</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -821,15 +821,15 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.5586305002882056</v>
+        <v>0.533651677207474</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.5694105527256875</v>
+        <v>0.5912030178017356</v>
       </c>
     </row>
     <row r="10">
@@ -840,32 +840,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ReeaL</t>
+          <t>Simp</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>26.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7656443519341345</v>
+        <v>0.623780160300653</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.7027545251056101</v>
+        <v>0.8290048852138072</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.6003244559127621</v>
+        <v>0.7454250373381728</v>
       </c>
     </row>
     <row r="11">
@@ -884,16 +884,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vikul</t>
+          <t>aBeZy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5362832218419846</v>
+        <v>0.6952442362617003</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.5830539448053725</v>
+        <v>0.8323677328453976</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.70094430107739</v>
+        <v>0.6293784114754173</v>
       </c>
     </row>
     <row r="12">
@@ -928,16 +928,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MettalZ</t>
+          <t>Drazah</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>25.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -945,15 +945,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5197175093404837</v>
+        <v>0.5609414707855791</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.5920739923081572</v>
+        <v>0.661579518625435</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.5683246443396923</v>
+        <v>0.6717428465186902</v>
       </c>
     </row>
     <row r="13">
@@ -972,16 +972,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Cellium</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>23.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.5543277787321997</v>
+        <v>0.5364983110756713</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.5825342641596204</v>
+        <v>0.6817616558401433</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.7139397806898299</v>
+        <v>0.5100878548896275</v>
       </c>
     </row>
     <row r="14">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JoeDeceives</t>
+          <t>CleanX</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.5</v>
+        <v>25.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.6058290813460186</v>
+        <v>0.7022013572310278</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.6488448184967844</v>
+        <v>0.8385139879694018</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.5119824981135206</v>
+        <v>0.6942790529679623</v>
       </c>
     </row>
     <row r="15">
@@ -1060,32 +1060,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kremp</t>
+          <t>Envoy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>23.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.5053835399445409</v>
+        <v>0.5574880088359135</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.6095114084440771</v>
+        <v>0.8401035661087912</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.60143840550315</v>
+        <v>0.5746760433420364</v>
       </c>
     </row>
     <row r="16">
@@ -1104,16 +1104,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ghosty</t>
+          <t>Scrap</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>26.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1121,15 +1121,15 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.5061114542189723</v>
+        <v>0.6536869980938438</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.6154443215846515</v>
+        <v>0.7042154545346471</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.6502066752686544</v>
+        <v>0.7691605389052645</v>
       </c>
     </row>
     <row r="17">
@@ -1148,16 +1148,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Search_and_Destroy</t>
+          <t>HardPoint</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nastie</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6.5</v>
+        <v>20.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.6032727317960439</v>
+        <v>0.529129717233573</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.5989734520017793</v>
+        <v>0.7883472920716644</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.5450828552578876</v>
+        <v>0.5182357710799547</v>
       </c>
     </row>
     <row r="18">
@@ -1192,40 +1192,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Search_and_Destroy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ReeaL</t>
+          <t>HyDra</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>7.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.6875014424051685</v>
+        <v>0.5180065845773154</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.5462394294944156</v>
+        <v>0.6514078226547148</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.5241304169882268</v>
+        <v>0.5012827882338275</v>
       </c>
     </row>
     <row r="19">
@@ -1236,24 +1236,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Search_and_Destroy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vikul</t>
+          <t>KiSMET</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>22.5</v>
+        <v>7.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.5915831173672174</v>
+        <v>0.6049331725406104</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.6952399108686945</v>
+        <v>0.5491461670782307</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.578708909349511</v>
+        <v>0.5183373618503819</v>
       </c>
     </row>
     <row r="20">
@@ -1280,16 +1280,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Search_and_Destroy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MettalZ</t>
+          <t>Sib</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21.5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.5934609173653927</v>
+        <v>0.5174689061815778</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1305,15 +1305,15 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.7549272401679014</v>
+        <v>0.5333304618869414</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.5222025324497285</v>
+        <v>0.5567509609306971</v>
       </c>
     </row>
     <row r="21">
@@ -1324,16 +1324,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Search_and_Destroy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Skyz</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.5407640902214814</v>
+        <v>0.5097379538505799</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1349,15 +1349,15 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.6976868167236704</v>
+        <v>0.6367252434980826</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.5777548134893487</v>
+        <v>0.5191622541345053</v>
       </c>
     </row>
     <row r="22">
@@ -1368,16 +1368,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Search_and_Destroy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JoeDeceives</t>
+          <t>Pred</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>7.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1385,15 +1385,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.7071491043586843</v>
+        <v>0.5613901654537543</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.5082910943262383</v>
+        <v>0.5098793825176139</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.5588392330797609</v>
+        <v>0.5203869610686018</v>
       </c>
     </row>
     <row r="23">
@@ -1412,16 +1412,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Search_and_Destroy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kremp</t>
+          <t>Shotzzy</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.5</v>
+        <v>7.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.5952929615477333</v>
+        <v>0.5670572984444552</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.5156978178031</v>
+        <v>0.6197787451844711</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.5295822575051504</v>
+        <v>0.5201713203688897</v>
       </c>
     </row>
     <row r="24">
@@ -1456,16 +1456,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Search_and_Destroy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ghosty</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.5</v>
+        <v>6.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.6886122430801519</v>
+        <v>0.5087343308418518</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.5220394020151609</v>
+        <v>0.5806239165240863</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.627630438187873</v>
+        <v>0.5387809288658254</v>
       </c>
     </row>
     <row r="25">
@@ -1500,40 +1500,1096 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dashy</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5025411868610081</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5794282253814576</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5510239266198578</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Simp</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5905168947377682</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6542466004756009</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5283467770247061</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>aBeZy</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5571702076933521</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6450497839403787</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5207461217029542</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Drazah</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.5135163093127904</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6039681686865565</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5561208013669142</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cellium</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5029728522134207</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6400317096703259</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5543749393818537</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CleanX</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5661303695836545</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6127786582502036</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5678539709640132</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Envoy</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5593452650400216</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0.547246829169604</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6066875100154523</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Scrap</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5431781607957894</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5867103564319186</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5745012029437185</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Search_and_Destroy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5530613091253879</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5530027990065115</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.5842583206824817</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nastie</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>22</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Under</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5919360960735772</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HyDra</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.6801644943961158</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6995964445625483</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.6154805064193228</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>KiSMET</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5278548235842091</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6631188815359322</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6106305252589145</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sib</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5256067748018605</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6489056364656138</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5680934320820598</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Skyz</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5420561430087064</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0.735733324785725</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5001659948489313</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pred</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.6470050566187932</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0.7599317143302622</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6366269908820681</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Shotzzy</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.6248893331964182</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0.755733012002779</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6410246141668494</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>Over</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>0.6393494075853796</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Under</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0.5368729566174919</v>
+      <c r="F40" t="n">
+        <v>0.6056440534506861</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7725078186336957</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.5339905399576926</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dashy</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5468939221609397</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0.7348242518941479</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5030525039352403</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Simp</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6465135811228399</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6860726388726971</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.5819907484507197</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>aBeZy</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>23</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.5867318794796095</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0.8076877597653418</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5789277818749767</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Drazah</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>24</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5068629508900795</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6424435292547885</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.5819907484507197</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cellium</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5546012001863637</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0.7367631049250551</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.5206272635037466</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CleanX</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.5167518787679237</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0.7583807003146783</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.6213649941945557</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Envoy</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>21</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5013769199932673</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0.7333520488071388</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.5013565013358824</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Scrap</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>25</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5756303770011525</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5882309997277265</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.569135203184989</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5/17/24</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.6204959030949244</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5779573625631518</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.5756675426406261</v>
       </c>
     </row>
   </sheetData>
